--- a/templates/office/EMP_EXE_010_비즈니스규칙사전정의서.xlsx
+++ b/templates/office/EMP_EXE_010_비즈니스규칙사전정의서.xlsx
@@ -515,7 +515,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>화장품 표시광고 AI 심의 룰셋, 금지어·주의어 사전 및 정규식 검증 규칙 명세</t>
+          <t>제품 표시·광고 AI 심의 룰셋, 금지어·주의어 사전 및 정규식 검증 규칙 명세</t>
         </is>
       </c>
     </row>
@@ -528,7 +528,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>아모레퍼시픽 AI 기반 화장품 표시광고 심의 및 리스크 예방 시스템 구축</t>
+          <t>한빛글로벌 엔터프라이즈 AI 콘텐츠·규제 심의 자동화 시스템(SyncGuard AI) 구축</t>
         </is>
       </c>
     </row>
@@ -576,7 +576,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>(주)아모레퍼시픽 (HANBIT GLOBAL)</t>
+          <t>㈜한빛글로벌 (Hanbit Global Corp.)</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>㈜그로브소프트 (EMPASY)</t>
+          <t>㈜엠파시 (Empasy Inc.)</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>화장품 규제대응(RA)팀 / 법무팀</t>
+          <t>컴플라이언스심의(RA)팀 / 법무팀</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
     <row r="2">
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>화장품 표시광고 심의 룰셋 마스터 (100 Rules)</t>
+          <t>제품 표시·광고 심의 룰셋 마스터 (100 Rules)</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>법적 근거 (화장품법 / 식약처)</t>
+          <t>법적 근거 (표시·광고 공정화법 / 식약처)</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>화장품법 제13조 제1항</t>
+          <t>표시·광고 공정화법 제3조 제1항</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="G6" s="9" t="inlineStr">
         <is>
-          <t>화장품법 제13조 제1항</t>
+          <t>표시·광고 공정화법 제3조 제1항</t>
         </is>
       </c>
       <c r="H6" s="9" t="inlineStr">
@@ -914,7 +914,7 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>화장품법 제13조</t>
+          <t>표시·광고 공정화법 제3조</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="G12" s="9" t="inlineStr">
         <is>
-          <t>화장품법 제13조</t>
+          <t>표시·광고 공정화법 제3조</t>
         </is>
       </c>
       <c r="H12" s="9" t="inlineStr">
@@ -1149,7 +1149,7 @@
       </c>
       <c r="G14" s="9" t="inlineStr">
         <is>
-          <t>화장품법 제13조</t>
+          <t>표시·광고 공정화법 제3조</t>
         </is>
       </c>
       <c r="H14" s="9" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>화장품법 제13조</t>
+          <t>표시·광고 공정화법 제3조</t>
         </is>
       </c>
       <c r="H16" s="9" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="G18" s="9" t="inlineStr">
         <is>
-          <t>화장품법 제13조</t>
+          <t>표시·광고 공정화법 제3조</t>
         </is>
       </c>
       <c r="H18" s="9" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="G20" s="9" t="inlineStr">
         <is>
-          <t>화장품법 제13조</t>
+          <t>표시·광고 공정화법 제3조</t>
         </is>
       </c>
       <c r="H20" s="9" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="G22" s="9" t="inlineStr">
         <is>
-          <t>화장품법 제13조</t>
+          <t>표시·광고 공정화법 제3조</t>
         </is>
       </c>
       <c r="H22" s="9" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="G24" s="9" t="inlineStr">
         <is>
-          <t>화장품법 제13조</t>
+          <t>표시·광고 공정화법 제3조</t>
         </is>
       </c>
       <c r="H24" s="9" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>아모레퍼시픽 최초</t>
+          <t>한빛글로벌 최초</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
@@ -1948,7 +1948,7 @@
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>화장품법 제13조</t>
+          <t>표시·광고 공정화법 제3조</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="G34" s="9" t="inlineStr">
         <is>
-          <t>화장품법 제13조</t>
+          <t>표시·광고 공정화법 제3조</t>
         </is>
       </c>
       <c r="H34" s="9" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>화장품법 제13조</t>
+          <t>표시·광고 공정화법 제3조</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>화장품법 제13조</t>
+          <t>표시·광고 공정화법 제3조</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="E40" s="9" t="inlineStr">
         <is>
-          <t>설화수 한방 의약</t>
+          <t>루미에르 한방 의약</t>
         </is>
       </c>
       <c r="F40" s="8" t="inlineStr">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="G40" s="9" t="inlineStr">
         <is>
-          <t>설화수 브랜드 헌장</t>
+          <t>루미에르 브랜드 헌장</t>
         </is>
       </c>
       <c r="H40" s="9" t="inlineStr">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>헤라 성형 쿠션</t>
+          <t>벨르코어 성형 쿠션</t>
         </is>
       </c>
       <c r="F41" s="7" t="inlineStr">
@@ -2418,7 +2418,7 @@
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>헤라 브랜드 가이드</t>
+          <t>벨르코어 브랜드 가이드</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="E42" s="9" t="inlineStr">
         <is>
-          <t>아이오페 레이저 세럼</t>
+          <t>바이오랩 레이저 세럼</t>
         </is>
       </c>
       <c r="F42" s="8" t="inlineStr">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="G42" s="9" t="inlineStr">
         <is>
-          <t>아이오페 톤앤매너</t>
+          <t>바이오랩 톤앤매너</t>
         </is>
       </c>
       <c r="H42" s="9" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>라네즈 마법 슬리핑</t>
+          <t>아쿠아퓨어 마법 슬리핑</t>
         </is>
       </c>
       <c r="F43" s="7" t="inlineStr">
@@ -2512,7 +2512,7 @@
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>라네즈 브랜드 가이드</t>
+          <t>아쿠아퓨어 브랜드 가이드</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="E44" s="9" t="inlineStr">
         <is>
-          <t>에스트라 약국 크림</t>
+          <t>더마쉴드 약국 크림</t>
         </is>
       </c>
       <c r="F44" s="8" t="inlineStr">
@@ -2559,7 +2559,7 @@
       </c>
       <c r="G44" s="9" t="inlineStr">
         <is>
-          <t>에스트라 가이드</t>
+          <t>더마쉴드 가이드</t>
         </is>
       </c>
       <c r="H44" s="9" t="inlineStr">
@@ -2653,7 +2653,7 @@
       </c>
       <c r="G46" s="9" t="inlineStr">
         <is>
-          <t>화장품법 제13조</t>
+          <t>표시·광고 공정화법 제3조</t>
         </is>
       </c>
       <c r="H46" s="9" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>화장품법 제13조</t>
+          <t>표시·광고 공정화법 제3조</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
@@ -2794,7 +2794,7 @@
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>화장품법 제13조</t>
+          <t>표시·광고 공정화법 제3조</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>화장품법 제13조</t>
+          <t>표시·광고 공정화법 제3조</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
@@ -2935,7 +2935,7 @@
       </c>
       <c r="G52" s="9" t="inlineStr">
         <is>
-          <t>화장품법 제13조</t>
+          <t>표시·광고 공정화법 제3조</t>
         </is>
       </c>
       <c r="H52" s="9" t="inlineStr">
@@ -3029,7 +3029,7 @@
       </c>
       <c r="G54" s="9" t="inlineStr">
         <is>
-          <t>화장품법 제13조</t>
+          <t>표시·광고 공정화법 제3조</t>
         </is>
       </c>
       <c r="H54" s="9" t="inlineStr">
@@ -3123,7 +3123,7 @@
       </c>
       <c r="G56" s="9" t="inlineStr">
         <is>
-          <t>화장품법 제13조</t>
+          <t>표시·광고 공정화법 제3조</t>
         </is>
       </c>
       <c r="H56" s="9" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t>화장품법 제13조</t>
+          <t>표시·광고 공정화법 제3조</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t>화장품법 제13조</t>
+          <t>표시·광고 공정화법 제3조</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>화장품법 제13조</t>
+          <t>표시·광고 공정화법 제3조</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr">
@@ -3405,7 +3405,7 @@
       </c>
       <c r="G62" s="9" t="inlineStr">
         <is>
-          <t>화장품법 제13조</t>
+          <t>표시·광고 공정화법 제3조</t>
         </is>
       </c>
       <c r="H62" s="9" t="inlineStr">
@@ -3499,7 +3499,7 @@
       </c>
       <c r="G64" s="9" t="inlineStr">
         <is>
-          <t>화장품법 제13조</t>
+          <t>표시·광고 공정화법 제3조</t>
         </is>
       </c>
       <c r="H64" s="9" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="G66" s="9" t="inlineStr">
         <is>
-          <t>화장품법 제13조</t>
+          <t>표시·광고 공정화법 제3조</t>
         </is>
       </c>
       <c r="H66" s="9" t="inlineStr">
@@ -3640,7 +3640,7 @@
       </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>화장품법 제13조</t>
+          <t>표시·광고 공정화법 제3조</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr">
@@ -3734,7 +3734,7 @@
       </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t>화장품법 제13조</t>
+          <t>표시·광고 공정화법 제3조</t>
         </is>
       </c>
       <c r="H69" s="4" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t>화장품법 제13조</t>
+          <t>표시·광고 공정화법 제3조</t>
         </is>
       </c>
       <c r="H71" s="4" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="G72" s="9" t="inlineStr">
         <is>
-          <t>화장품법 제13조</t>
+          <t>표시·광고 공정화법 제3조</t>
         </is>
       </c>
       <c r="H72" s="9" t="inlineStr">
@@ -3969,7 +3969,7 @@
       </c>
       <c r="G74" s="9" t="inlineStr">
         <is>
-          <t>화장품법 제13조</t>
+          <t>표시·광고 공정화법 제3조</t>
         </is>
       </c>
       <c r="H74" s="9" t="inlineStr">
@@ -4063,7 +4063,7 @@
       </c>
       <c r="G76" s="9" t="inlineStr">
         <is>
-          <t>화장품법 제13조</t>
+          <t>표시·광고 공정화법 제3조</t>
         </is>
       </c>
       <c r="H76" s="9" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="G77" s="4" t="inlineStr">
         <is>
-          <t>화장품법 제13조</t>
+          <t>표시·광고 공정화법 제3조</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="G79" s="4" t="inlineStr">
         <is>
-          <t>화장품법 제13조</t>
+          <t>표시·광고 공정화법 제3조</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr">
@@ -4298,7 +4298,7 @@
       </c>
       <c r="G81" s="4" t="inlineStr">
         <is>
-          <t>화장품법 제13조</t>
+          <t>표시·광고 공정화법 제3조</t>
         </is>
       </c>
       <c r="H81" s="4" t="inlineStr">
@@ -4345,7 +4345,7 @@
       </c>
       <c r="G82" s="9" t="inlineStr">
         <is>
-          <t>화장품법 제13조</t>
+          <t>표시·광고 공정화법 제3조</t>
         </is>
       </c>
       <c r="H82" s="9" t="inlineStr">
@@ -4439,7 +4439,7 @@
       </c>
       <c r="G84" s="9" t="inlineStr">
         <is>
-          <t>화장품법 제13조</t>
+          <t>표시·광고 공정화법 제3조</t>
         </is>
       </c>
       <c r="H84" s="9" t="inlineStr">
@@ -4533,7 +4533,7 @@
       </c>
       <c r="G86" s="9" t="inlineStr">
         <is>
-          <t>화장품법 제13조</t>
+          <t>표시·광고 공정화법 제3조</t>
         </is>
       </c>
       <c r="H86" s="9" t="inlineStr">
@@ -4580,7 +4580,7 @@
       </c>
       <c r="G87" s="4" t="inlineStr">
         <is>
-          <t>화장품법 제13조</t>
+          <t>표시·광고 공정화법 제3조</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr">
@@ -4674,7 +4674,7 @@
       </c>
       <c r="G89" s="4" t="inlineStr">
         <is>
-          <t>화장품법 제13조</t>
+          <t>표시·광고 공정화법 제3조</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="G91" s="4" t="inlineStr">
         <is>
-          <t>화장품법 제13조</t>
+          <t>표시·광고 공정화법 제3조</t>
         </is>
       </c>
       <c r="H91" s="4" t="inlineStr">
@@ -4815,7 +4815,7 @@
       </c>
       <c r="G92" s="9" t="inlineStr">
         <is>
-          <t>화장품법 제13조</t>
+          <t>표시·광고 공정화법 제3조</t>
         </is>
       </c>
       <c r="H92" s="9" t="inlineStr">
@@ -4909,7 +4909,7 @@
       </c>
       <c r="G94" s="9" t="inlineStr">
         <is>
-          <t>화장품법 제13조</t>
+          <t>표시·광고 공정화법 제3조</t>
         </is>
       </c>
       <c r="H94" s="9" t="inlineStr">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="G96" s="9" t="inlineStr">
         <is>
-          <t>화장품법 제13조</t>
+          <t>표시·광고 공정화법 제3조</t>
         </is>
       </c>
       <c r="H96" s="9" t="inlineStr">
@@ -5050,7 +5050,7 @@
       </c>
       <c r="G97" s="4" t="inlineStr">
         <is>
-          <t>화장품법 제13조</t>
+          <t>표시·광고 공정화법 제3조</t>
         </is>
       </c>
       <c r="H97" s="4" t="inlineStr">
@@ -5144,7 +5144,7 @@
       </c>
       <c r="G99" s="4" t="inlineStr">
         <is>
-          <t>화장품법 제13조</t>
+          <t>표시·광고 공정화법 제3조</t>
         </is>
       </c>
       <c r="H99" s="4" t="inlineStr">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="G101" s="4" t="inlineStr">
         <is>
-          <t>화장품법 제13조</t>
+          <t>표시·광고 공정화법 제3조</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr">
@@ -5285,7 +5285,7 @@
       </c>
       <c r="G102" s="9" t="inlineStr">
         <is>
-          <t>화장품법 제13조</t>
+          <t>표시·광고 공정화법 제3조</t>
         </is>
       </c>
       <c r="H102" s="9" t="inlineStr">
@@ -5379,7 +5379,7 @@
       </c>
       <c r="G104" s="9" t="inlineStr">
         <is>
-          <t>화장품법 제13조</t>
+          <t>표시·광고 공정화법 제3조</t>
         </is>
       </c>
       <c r="H104" s="9" t="inlineStr">
